--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_concproduct_Auto.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_concproduct_Auto.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>591.1889053626226</v>
+        <v>577.356496205107</v>
       </c>
       <c r="C2">
-        <v>370.7240588753158</v>
+        <v>377.2421793673952</v>
       </c>
       <c r="D2">
-        <v>312.0760440438578</v>
+        <v>311.9025544230031</v>
       </c>
       <c r="E2">
-        <v>274.6007624900781</v>
+        <v>280.8172632168321</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>706.5395298251274</v>
+        <v>665.4672306722459</v>
       </c>
       <c r="C3">
-        <v>440.5443958823473</v>
+        <v>437.3520700051627</v>
       </c>
       <c r="D3">
-        <v>367.5404322105072</v>
+        <v>364.5931336567064</v>
       </c>
       <c r="E3">
-        <v>326.0277131780949</v>
+        <v>331.9375435726485</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>715.104855038558</v>
+        <v>645.5396424835536</v>
       </c>
       <c r="C4">
-        <v>442.7858582055435</v>
+        <v>422.3197612176289</v>
       </c>
       <c r="D4">
-        <v>367.1781300116165</v>
+        <v>352.7619727517598</v>
       </c>
       <c r="E4">
-        <v>325.1895444952996</v>
+        <v>321.5394622964359</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>544.2958329054586</v>
+        <v>460.370649390654</v>
       </c>
       <c r="C5">
-        <v>323.777547441535</v>
+        <v>299.1221545791591</v>
       </c>
       <c r="D5">
-        <v>257.8501257606252</v>
+        <v>244.4989282820456</v>
       </c>
       <c r="E5">
-        <v>228.2999937279844</v>
+        <v>224.0371958427168</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>481.1783049099778</v>
+        <v>444.2851381247584</v>
       </c>
       <c r="C6">
-        <v>285.498380909673</v>
+        <v>274.0640067074119</v>
       </c>
       <c r="D6">
-        <v>229.1516582824211</v>
+        <v>218.890975883912</v>
       </c>
       <c r="E6">
-        <v>200.2069709732835</v>
+        <v>197.216208676166</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>54.83687935742709</v>
+        <v>43.79550304582345</v>
       </c>
       <c r="C7">
-        <v>31.23958445848835</v>
+        <v>28.19043601991935</v>
       </c>
       <c r="D7">
-        <v>24.6275564913649</v>
+        <v>23.29443868700433</v>
       </c>
       <c r="E7">
-        <v>21.21652799865949</v>
+        <v>20.91996284012</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1331.242707437316</v>
+        <v>2240.976194357066</v>
       </c>
       <c r="C8">
-        <v>1096.965321119154</v>
+        <v>1386.974704974449</v>
       </c>
       <c r="D8">
-        <v>1036.678090764719</v>
+        <v>1167.014165702147</v>
       </c>
       <c r="E8">
-        <v>1058.730947649033</v>
+        <v>1079.7131497476</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>624.5632035571949</v>
+        <v>551.318372037128</v>
       </c>
       <c r="C9">
-        <v>385.5847459911028</v>
+        <v>363.7102176105692</v>
       </c>
       <c r="D9">
-        <v>319.1188920320096</v>
+        <v>305.7924834665243</v>
       </c>
       <c r="E9">
-        <v>282.766790364518</v>
+        <v>279.500088567154</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>320.0298880488805</v>
+        <v>244.2138551302405</v>
       </c>
       <c r="C10">
-        <v>179.2592538594662</v>
+        <v>158.4617140933626</v>
       </c>
       <c r="D10">
-        <v>142.6037805361524</v>
+        <v>133.3524500112542</v>
       </c>
       <c r="E10">
-        <v>121.2436951680542</v>
+        <v>118.33617664089</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>60.50120700807455</v>
+        <v>45.91022539218498</v>
       </c>
       <c r="C11">
-        <v>31.59537102645284</v>
+        <v>27.90136882217155</v>
       </c>
       <c r="D11">
-        <v>24.69471916938721</v>
+        <v>23.10162090392851</v>
       </c>
       <c r="E11">
-        <v>22.62977408003403</v>
+        <v>22.11439706454975</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>139.3682673508568</v>
+        <v>104.0755140178866</v>
       </c>
       <c r="C12">
-        <v>82.34358140592862</v>
+        <v>72.09794916017451</v>
       </c>
       <c r="D12">
-        <v>65.23333897258401</v>
+        <v>60.81907881873739</v>
       </c>
       <c r="E12">
-        <v>54.8065742470489</v>
+        <v>53.37108057718023</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>179.2266158371582</v>
+        <v>136.1841753323431</v>
       </c>
       <c r="C13">
-        <v>99.8274982845073</v>
+        <v>88.01317346988841</v>
       </c>
       <c r="D13">
-        <v>80.20582558385681</v>
+        <v>74.91618632150265</v>
       </c>
       <c r="E13">
-        <v>69.00605023841192</v>
+        <v>67.28517365038661</v>
       </c>
     </row>
   </sheetData>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_concproduct_Auto.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_concproduct_Auto.xlsx
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>460.370649390654</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>299.1221545791591</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>244.4989282820456</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>224.0371958427168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2240.976194357066</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>1386.974704974449</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1167.014165702147</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>1079.7131497476</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>244.2138551302405</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>158.4617140933626</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>133.3524500112542</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>118.33617664089</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>45.91022539218498</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>27.90136882217155</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>23.10162090392851</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>22.11439706454975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>136.1841753323431</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>88.01317346988841</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>74.91618632150265</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>67.28517365038661</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
